--- a/1. MSR Creator/ControlFile_MSRCreator.xlsx
+++ b/1. MSR Creator/ControlFile_MSRCreator.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Desktop\Model-Supply-Regions-MSR-Toolset\1. MSR Creator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\1. MSR Creator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA20CB0-B688-4422-A204-B1640FCEB711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE40662-20C0-4EBC-8957-71C3C1A644A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23880" yWindow="-6870" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paths" sheetId="9" r:id="rId1"/>
@@ -35,6 +35,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -589,12 +592,6 @@
     <t>Enter turbine nameplate capacity in exponential form (kW) e.g. enter 1.96e6 for 1.96MW</t>
   </si>
   <si>
-    <t>C:\Users\Carlos\Desktop\Model-Supply-Regions-MSR-Toolset\1. MSR Creator</t>
-  </si>
-  <si>
-    <t>C:\Users\Carlos\Desktop\Model-Supply-Regions-MSR-Toolset\countrynames.csv</t>
-  </si>
-  <si>
     <t>Pixels below this value will be disregarded. Value can be changed by code if iterative relaxer mode is on. Units: m/s (****initially 6, but changed to include more surface)</t>
   </si>
   <si>
@@ -608,6 +605,12 @@
   </si>
   <si>
     <t>solarpv</t>
+  </si>
+  <si>
+    <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\1. MSR Creator</t>
+  </si>
+  <si>
+    <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\countrynames.csv</t>
   </si>
 </sst>
 </file>
@@ -1037,7 +1040,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -1070,7 +1073,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
@@ -1123,7 +1126,7 @@
         <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
@@ -1134,7 +1137,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1175,7 +1178,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>24</v>
@@ -2352,7 +2355,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2407,7 +2410,7 @@
         <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">

--- a/1. MSR Creator/ControlFile_MSRCreator.xlsx
+++ b/1. MSR Creator/ControlFile_MSRCreator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\1. MSR Creator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEE40662-20C0-4EBC-8957-71C3C1A644A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F023BA0-03A8-4520-93A5-BA2B32C98289}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23880" yWindow="-6870" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23880" yWindow="-6870" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paths" sheetId="9" r:id="rId1"/>
@@ -604,13 +604,13 @@
     <t>Options=[0-No, 1-Yes]. Relax resource thresholds for resource lagging countries (***initially 0, but changed due to the mountain regions of Bolivia)</t>
   </si>
   <si>
-    <t>solarpv</t>
-  </si>
-  <si>
     <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\1. MSR Creator</t>
   </si>
   <si>
     <t>C:\Users\Carlos\Desktop\MSR\Model-Supply-Regions-MSR-Toolset\countrynames.csv</t>
+  </si>
+  <si>
+    <t>wind</t>
   </si>
 </sst>
 </file>
@@ -1040,7 +1040,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -1073,7 +1073,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>12</v>
@@ -1178,7 +1178,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>24</v>
@@ -2352,7 +2352,7 @@
         <v>122</v>
       </c>
       <c r="B6" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>173</v>
@@ -2363,7 +2363,7 @@
         <v>123</v>
       </c>
       <c r="B7" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>124</v>
